--- a/STTM.xlsx
+++ b/STTM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msado\SynologyDrive\Studia\Hurtownie danych\Deweloperzy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE565A0-2A57-4A7D-915D-DB93ADECBD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21274A97-D21E-43FB-A30A-212E9FCC878F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{A8DCC76A-9357-4B42-AF62-F275E4EE0011}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="218">
   <si>
     <t>FK</t>
   </si>
@@ -284,9 +284,6 @@
     <t>Średnie wynagrodzenie</t>
   </si>
   <si>
-    <t>18, 3</t>
-  </si>
-  <si>
     <t>Plik Wynagrodzenia_regionalne.xlsx</t>
   </si>
   <si>
@@ -392,9 +389,6 @@
     <t>Sprzedaż produkcji budowlano-montażowej w budowie budynków w danej jednostce</t>
   </si>
   <si>
-    <t>5, 1</t>
-  </si>
-  <si>
     <t>Wartości po UNPIVOT</t>
   </si>
   <si>
@@ -452,15 +446,9 @@
     <t>Średnie oprocentowanie kredytu</t>
   </si>
   <si>
-    <t>5, 3</t>
-  </si>
-  <si>
     <t>4 OPN2PLN</t>
   </si>
   <si>
-    <t>5 OPN2PLN</t>
-  </si>
-  <si>
     <t>Nagłówki kolumn</t>
   </si>
   <si>
@@ -695,10 +683,25 @@
     <t>Pobierz unikalne wartości z kolumny Jednostka</t>
   </si>
   <si>
-    <t>Plik Stopy_procentowe.xlsx</t>
-  </si>
-  <si>
-    <t>Plik Stopy_procentowe.xslx</t>
+    <t>Lookup wartości ID na podstawie regionu</t>
+  </si>
+  <si>
+    <t>18, 2</t>
+  </si>
+  <si>
+    <t>5, 2</t>
+  </si>
+  <si>
+    <t>Plik Stopy_procentowe.csv</t>
+  </si>
+  <si>
+    <t>NazwaOryginalna</t>
+  </si>
+  <si>
+    <t>Przeciętne miesięczne wynagrodzenie nominalne brutto w gospodarce narodowej</t>
+  </si>
+  <si>
+    <t>Całkowita nazwa wiersza wczytana z pliku</t>
   </si>
 </sst>
 </file>
@@ -708,7 +711,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;zł&quot;;[Red]\-#,##0\ &quot;zł&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -780,6 +783,19 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -1017,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1150,6 +1166,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1724,7 +1770,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.35">
@@ -1762,14 +1808,14 @@
         <v>59</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R9" s="33"/>
     </row>
@@ -1808,14 +1854,14 @@
         <v>61</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R10" s="33"/>
     </row>
@@ -1860,7 +1906,9 @@
       <c r="P11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="Q11" s="14"/>
+      <c r="Q11" s="14" t="s">
+        <v>211</v>
+      </c>
       <c r="R11" s="33"/>
     </row>
     <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.35">
@@ -1900,7 +1948,7 @@
       </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q12" s="14" t="s">
         <v>66</v>
@@ -1944,7 +1992,7 @@
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q13" s="14" t="s">
         <v>66</v>
@@ -1986,14 +2034,14 @@
         <v>65</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R14" s="33"/>
     </row>
@@ -2034,7 +2082,7 @@
       </c>
       <c r="O15" s="36"/>
       <c r="P15" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q15" s="14" t="s">
         <v>66</v>
@@ -2078,7 +2126,7 @@
       </c>
       <c r="O16" s="36"/>
       <c r="P16" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q16" s="14" t="s">
         <v>66</v>
@@ -2122,7 +2170,7 @@
       </c>
       <c r="O17" s="36"/>
       <c r="P17" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q17" s="14" t="s">
         <v>66</v>
@@ -2168,7 +2216,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -2192,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -2216,7 +2264,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -2240,7 +2288,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -2335,7 +2383,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L7" s="32" t="s">
         <v>52</v>
@@ -2362,10 +2410,10 @@
     </row>
     <row r="8" spans="1:19" ht="20" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -2395,24 +2443,24 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="30" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E9" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -2421,27 +2469,27 @@
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K9" s="13">
         <v>1</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
@@ -2727,10 +2775,10 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="20" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -2758,7 +2806,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>64</v>
@@ -2773,7 +2821,9 @@
       <c r="P9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="Q9" s="14"/>
+      <c r="Q9" s="14" t="s">
+        <v>211</v>
+      </c>
       <c r="R9" s="33"/>
     </row>
     <row r="10" spans="1:18" ht="30" x14ac:dyDescent="0.35">
@@ -2804,7 +2854,7 @@
         <v>41</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>64</v>
@@ -2813,14 +2863,14 @@
         <v>59</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R10" s="33"/>
     </row>
@@ -2838,7 +2888,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -2850,7 +2900,7 @@
         <v>2507.77</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>64</v>
@@ -2859,14 +2909,14 @@
         <v>65</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R11" s="33"/>
     </row>
@@ -3008,7 +3058,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -3054,7 +3104,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -3077,7 +3127,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -3193,10 +3243,10 @@
     </row>
     <row r="8" spans="1:18" ht="30" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -3223,18 +3273,18 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="40" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
@@ -3244,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>1</v>
@@ -3254,21 +3304,21 @@
         <v>2</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R9" s="33"/>
     </row>
@@ -3300,33 +3350,33 @@
         <v>41</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R10" s="33"/>
     </row>
     <row r="11" spans="1:18" ht="40" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>3</v>
@@ -3336,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>1</v>
@@ -3346,21 +3396,21 @@
         <v>41</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R11" s="33"/>
     </row>
@@ -3378,7 +3428,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -3390,21 +3440,21 @@
         <v>2507.77</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R12" s="33"/>
     </row>
@@ -3546,7 +3596,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -3592,7 +3642,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -3615,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -3731,10 +3781,10 @@
     </row>
     <row r="8" spans="1:18" ht="30" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -3761,7 +3811,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="50" x14ac:dyDescent="0.35">
@@ -3792,33 +3842,33 @@
         <v>41</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R9" s="33"/>
     </row>
     <row r="10" spans="1:18" ht="40" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
@@ -3828,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>1</v>
@@ -3838,33 +3888,33 @@
         <v>41</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R10" s="33"/>
     </row>
     <row r="11" spans="1:18" ht="70" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>3</v>
@@ -3880,33 +3930,33 @@
         <v>24500</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R11" s="33"/>
     </row>
     <row r="12" spans="1:18" ht="70" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>3</v>
@@ -3922,33 +3972,33 @@
         <v>20800</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R12" s="33"/>
     </row>
     <row r="13" spans="1:18" ht="70" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>3</v>
@@ -3964,33 +4014,33 @@
         <v>675200</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R13" s="33"/>
     </row>
     <row r="14" spans="1:18" ht="70" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>3</v>
@@ -4006,39 +4056,39 @@
         <v>18000</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R14" s="33"/>
     </row>
     <row r="15" spans="1:18" ht="60" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>114</v>
+        <v>213</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -4050,21 +4100,21 @@
         <v>105.1</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R15" s="33"/>
     </row>
@@ -4149,7 +4199,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -4195,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -4218,7 +4268,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -4334,10 +4384,10 @@
     </row>
     <row r="8" spans="1:18" ht="20" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>29</v>
@@ -4364,7 +4414,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="50" x14ac:dyDescent="0.35">
@@ -4395,41 +4445,41 @@
         <v>41</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="R9" s="33"/>
     </row>
     <row r="10" spans="1:18" ht="150" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -4438,28 +4488,28 @@
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="2">
-        <v>7.5999999999999998E-2</v>
+        <v>7.6</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="R10" s="33"/>
     </row>
@@ -4603,7 +4653,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -4627,7 +4677,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -4651,7 +4701,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -4675,7 +4725,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -4770,7 +4820,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L7" s="32" t="s">
         <v>52</v>
@@ -4830,21 +4880,21 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="30" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E9" s="3">
         <v>50</v>
@@ -4856,7 +4906,7 @@
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K9" s="18">
         <v>1</v>
@@ -4868,10 +4918,10 @@
         <v>64</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="4" t="s">
@@ -4882,16 +4932,16 @@
     </row>
     <row r="10" spans="1:19" ht="40" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4">
         <v>50</v>
@@ -4903,7 +4953,7 @@
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K10" s="18">
         <v>1</v>
@@ -4915,10 +4965,10 @@
         <v>64</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4" t="s">
@@ -5073,7 +5123,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -5097,7 +5147,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -5121,7 +5171,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -5145,7 +5195,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -5240,7 +5290,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L7" s="32" t="s">
         <v>52</v>
@@ -5300,18 +5350,18 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="20" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>3</v>
@@ -5330,7 +5380,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="2" t="s">
@@ -5347,16 +5397,16 @@
     </row>
     <row r="10" spans="1:19" ht="20" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4">
         <v>50</v>
@@ -5368,20 +5418,20 @@
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K10" s="13">
         <v>2</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4" t="s">
@@ -5391,16 +5441,16 @@
     </row>
     <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E11" s="4">
         <v>50</v>
@@ -5412,20 +5462,20 @@
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K11" s="13">
         <v>2</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4" t="s">
@@ -5435,16 +5485,16 @@
     </row>
     <row r="12" spans="1:19" ht="40" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -5466,21 +5516,21 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="13" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="40" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -5504,21 +5554,21 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="50" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
@@ -5542,7 +5592,7 @@
       <c r="P14" s="36"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
@@ -5616,7 +5666,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -5640,7 +5690,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -5664,7 +5714,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -5688,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -5783,7 +5833,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L7" s="32" t="s">
         <v>52</v>
@@ -5843,18 +5893,18 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="13" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="30" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>3</v>
@@ -5873,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="2"/>
@@ -5881,18 +5931,18 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="30" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>3</v>
@@ -5911,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="2"/>
@@ -5919,18 +5969,18 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="13" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="40" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>3</v>
@@ -5949,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="2"/>
@@ -5957,21 +6007,21 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="13" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E12" s="4">
         <v>50</v>
@@ -5983,13 +6033,13 @@
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="19" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K12" s="13">
         <v>1</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="2"/>
@@ -5997,7 +6047,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
@@ -6070,7 +6120,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -6094,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -6118,7 +6168,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
@@ -6142,7 +6192,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -6237,7 +6287,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L7" s="32" t="s">
         <v>52</v>
@@ -6263,150 +6313,179 @@
       <c r="S7" s="33"/>
     </row>
     <row r="8" spans="1:19" ht="20" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="A8" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="46"/>
+      <c r="F8" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="2" t="s">
+      <c r="G8" s="46"/>
+      <c r="H8" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="46"/>
+      <c r="J8" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="K8" s="13">
-        <v>1</v>
-      </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="13" t="s">
+      <c r="K8" s="47">
+        <v>1</v>
+      </c>
+      <c r="L8" s="48"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="50" x14ac:dyDescent="0.35">
+      <c r="A9" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="46">
+        <v>100</v>
+      </c>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="46"/>
+      <c r="J9" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="K9" s="47">
+        <v>1</v>
+      </c>
+      <c r="L9" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="46"/>
+      <c r="N9" s="45" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" ht="50" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="O9" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="4">
-        <v>50</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="K9" s="13">
-        <v>1</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="O9" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="10" spans="1:19" ht="30" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="46">
+        <v>100</v>
+      </c>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="46"/>
+      <c r="J10" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="K10" s="47">
+        <v>1</v>
+      </c>
+      <c r="L10" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="46"/>
+      <c r="N10" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" s="4">
-        <v>50</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="K10" s="13">
-        <v>1</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="8"/>
+    </row>
+    <row r="11" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="50">
+        <v>255</v>
+      </c>
+      <c r="F11" s="37"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="37"/>
+      <c r="J11" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" s="53">
+        <v>1</v>
+      </c>
+      <c r="L11" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="46"/>
+      <c r="N11" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="52"/>
+      <c r="S11" s="33"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
@@ -6430,5 +6509,6 @@
     <mergeCell ref="L6:R6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>